--- a/Assets/Resources/Excels/Definition.xlsx
+++ b/Assets/Resources/Excels/Definition.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Project\Assets\Resources\Excels\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\NDC\Assets\Resources\Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E404DDE-BD20-459F-8BC6-8BAD4352F13C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CFBC526-0078-4C86-99AF-C9E1A91A6E2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Lock" sheetId="10" r:id="rId1"/>
@@ -29,17 +29,6 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
@@ -52,10 +41,19 @@
   <commentList>
     <comment ref="D1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000001000000}">
       <text>
-        <t>[스레드 댓글]
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="맑은 고딕"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>[스레드 댓글]
 사용 중인 버전의 Excel에서 이 스레드 댓글을 읽을 수 있지만 파일을 이후 버전의 Excel에서 열면 편집 내용이 모두 제거됩니다. 자세한 정보: https://go.microsoft.com/fwlink/?linkid=870924.
 댓글:
     유저가 처음 갖고 시작하는 양</t>
+        </r>
       </text>
     </comment>
   </commentList>
@@ -2090,13 +2088,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F35"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999"/>
   <cols>
-    <col min="1" max="1" width="25.375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.75" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.125" style="14" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.25" style="14" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.625" style="5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="25.3984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.69921875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.09765625" style="14" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.19921875" style="14" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.59765625" style="5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -2806,17 +2804,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:J38"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999"/>
   <cols>
     <col min="1" max="1" width="29.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="6" width="13.875" customWidth="1"/>
+    <col min="2" max="2" width="8.09765625" bestFit="1" customWidth="1"/>
+    <col min="3" max="6" width="13.8984375" customWidth="1"/>
     <col min="8" max="8" width="32.5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="72.75" style="6" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="72.69921875" style="6" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="17.25" thickBot="1">
+    <row r="1" spans="1:9" ht="18" thickBot="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3839,17 +3837,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:E8"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999"/>
   <cols>
-    <col min="1" max="1" width="21.875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="30.875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="30.875" customWidth="1"/>
-    <col min="5" max="5" width="25.25" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.75" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.8984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.8984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="30.8984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="30.8984375" customWidth="1"/>
+    <col min="5" max="5" width="25.19921875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.69921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="17.25" thickBot="1">
+    <row r="1" spans="1:5" ht="18" thickBot="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3992,19 +3990,19 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:J84"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999"/>
   <cols>
-    <col min="1" max="1" width="30.875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.125" customWidth="1"/>
-    <col min="4" max="4" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.25" customWidth="1"/>
-    <col min="6" max="6" width="8.625" customWidth="1"/>
-    <col min="7" max="7" width="28.75" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.8984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.09765625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.09765625" customWidth="1"/>
+    <col min="4" max="4" width="11.19921875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.19921875" customWidth="1"/>
+    <col min="6" max="6" width="8.59765625" customWidth="1"/>
+    <col min="7" max="7" width="28.69921875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="25.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="17.25" thickBot="1">
+    <row r="1" spans="1:10" ht="18" thickBot="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6161,13 +6159,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:D8"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999"/>
   <cols>
-    <col min="1" max="1" width="11.375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.3984375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="17.25" thickBot="1">
+    <row r="1" spans="1:4" ht="18" thickBot="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6265,12 +6263,12 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999"/>
   <cols>
     <col min="1" max="1" width="18.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="17.25" thickBot="1">
+    <row r="1" spans="1:3" ht="18" thickBot="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6334,13 +6332,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:D22"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999"/>
   <cols>
-    <col min="1" max="1" width="32.75" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="33.125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32.69921875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="33.09765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="17.25" thickBot="1">
+    <row r="1" spans="1:3" ht="18" thickBot="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6375,7 +6373,7 @@
         <v>87</v>
       </c>
       <c r="B4">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="C4" t="s">
         <v>88</v>
